--- a/Collections/United_Kingdom/#United_Kingdom#After_DecimalDay#Regular#[1968-present]#circulation_quality.xlsx
+++ b/Collections/United_Kingdom/#United_Kingdom#After_DecimalDay#Regular#[1968-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\United_Kingdom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10991CB-4EA8-47CB-9BB4-16725B058483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35218AC8-0F76-4778-AB5B-3B13645A318F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="halfpence" sheetId="26" r:id="rId1"/>
@@ -2125,14 +2125,15 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="184">
+  <dxfs count="150">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -3310,279 +3311,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3611,9 +3339,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="183"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="182" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="181"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4050,7 +3778,7 @@
         <v>22</v>
       </c>
       <c r="F6" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="5" t="str">
         <f>IF(OR(AND(F6&gt;1,F6&lt;&gt;"-")),"Can exchange","")</f>
@@ -4170,7 +3898,7 @@
         <v>16</v>
       </c>
       <c r="F11" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4314,7 +4042,7 @@
         <v>24</v>
       </c>
       <c r="F17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5359,7 +5087,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F6 F8 F10 F12 F14 F16 F18">
+  <conditionalFormatting sqref="F8 F6 F10 F12 F14 F16 F18">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5372,11 +5100,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6 F8 F10 F12 F14 F16 F18">
-    <cfRule type="containsText" dxfId="180" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="149" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F9 F11 F13 F15 F17">
+  <conditionalFormatting sqref="F11 F9 F13 F15 F17">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5389,7 +5117,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9 F11 F13 F15 F17">
-    <cfRule type="containsText" dxfId="179" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="148" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5406,7 +5134,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="containsText" dxfId="178" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="147" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5423,7 +5151,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="177" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="146" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7120,7 +6848,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6 H8 H10 H12 H14 H16 H18 H20 H22 H24 H26 H29 H31 H33 H35 H37 H39 H41 H43 H50 H52 H55 H45 H47:H48">
+  <conditionalFormatting sqref="H8 H6 H10 H12 H14 H16 H18 H20 H22 H24 H26 H29 H31 H33 H35 H37 H39 H41 H43 H50 H52 H55 H45 H47:H48">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7133,11 +6861,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6 H8 H10 H12 H14 H16 H18 H20 H22 H24 H26 H29 H31 H33 H35 H37 H39 H41 H43 H50 H52 H55 H45 H47:H48">
-    <cfRule type="containsText" dxfId="176" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="145" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H9 H11 H13 H15 H17 H19 H21 H23 H25 H30 H32 H34 H36 H38 H40 H42 H49 H51 H54 H44 H46">
+  <conditionalFormatting sqref="H11 H9 H13 H15 H17 H19 H21 H23 H25 H30 H32 H34 H36 H38 H40 H42 H49 H51 H54 H44 H46">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7150,7 +6878,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9 H11 H13 H15 H17 H19 H21 H23 H25 H30 H32 H34 H36 H38 H40 H42 H49 H51 H54 H44 H46">
-    <cfRule type="containsText" dxfId="175" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="144" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7167,7 +6895,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="174" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="143" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7184,7 +6912,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="173" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="142" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7201,12 +6929,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H56">
-    <cfRule type="containsText" dxfId="172" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="141" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H56))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H53">
-    <cfRule type="containsText" dxfId="171" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="140" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7235,7 +6963,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7">
-    <cfRule type="containsText" dxfId="170" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="139" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7252,7 +6980,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H59">
-    <cfRule type="containsText" dxfId="169" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="138" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7269,7 +6997,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H58">
-    <cfRule type="containsText" dxfId="168" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="137" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7298,7 +7026,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H60">
-    <cfRule type="containsText" dxfId="167" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="136" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7315,12 +7043,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H57">
-    <cfRule type="containsText" dxfId="166" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="135" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H57))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H61">
-    <cfRule type="containsText" dxfId="165" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="134" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7349,7 +7077,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H62">
-    <cfRule type="containsText" dxfId="162" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="133" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H62))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7366,12 +7094,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H63">
-    <cfRule type="containsText" dxfId="161" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="132" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H63))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H64">
-    <cfRule type="containsText" dxfId="160" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="131" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H64))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9129,7 +8857,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6 H10 H12 H14 H16 H20 H22 H24 H26 H29 H31 H33 H36 H38 H40 H42 H44 H51 H53 H56 H46 H48:H49">
+  <conditionalFormatting sqref="H10 H6 H12 H14 H16 H20 H22 H24 H26 H29 H31 H33 H36 H38 H40 H42 H44 H51 H53 H56 H46 H48:H49">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9142,11 +8870,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6 H10 H12 H14 H16 H20 H22 H24 H26 H29 H31 H33 H36 H38 H40 H42 H44 H51 H53 H56 H46 H48:H49">
-    <cfRule type="containsText" dxfId="159" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="130" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11 H13 H15 H21 H23 H25 H30 H32 H35 H37 H39 H41 H43 H50 H52 H55 H45 H47">
+  <conditionalFormatting sqref="H13 H11 H15 H21 H23 H25 H30 H32 H35 H37 H39 H41 H43 H50 H52 H55 H45 H47">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9159,7 +8887,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11 H13 H15 H21 H23 H25 H30 H32 H35 H37 H39 H41 H43 H50 H52 H55 H45 H47">
-    <cfRule type="containsText" dxfId="158" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="129" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9176,7 +8904,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:H9">
-    <cfRule type="containsText" dxfId="157" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="128" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9193,7 +8921,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="156" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="127" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9210,7 +8938,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27">
-    <cfRule type="containsText" dxfId="155" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="126" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9227,7 +8955,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H57">
-    <cfRule type="containsText" dxfId="154" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="125" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H57))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9244,7 +8972,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H54">
-    <cfRule type="containsText" dxfId="153" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="124" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9261,7 +8989,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="containsText" dxfId="152" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="123" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9278,7 +9006,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18">
-    <cfRule type="containsText" dxfId="151" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="122" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H18))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9295,7 +9023,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19">
-    <cfRule type="containsText" dxfId="150" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="121" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9312,7 +9040,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34">
-    <cfRule type="containsText" dxfId="149" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="120" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9353,12 +9081,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H60">
-    <cfRule type="containsText" dxfId="148" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="119" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H61">
-    <cfRule type="containsText" dxfId="147" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="118" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H61))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9375,7 +9103,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H59">
-    <cfRule type="containsText" dxfId="146" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="117" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H59))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9392,12 +9120,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H58">
-    <cfRule type="containsText" dxfId="145" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="116" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H58))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H65">
-    <cfRule type="containsText" dxfId="141" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="115" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H65))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9414,12 +9142,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H62">
-    <cfRule type="containsText" dxfId="134" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="114" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H62))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H63">
-    <cfRule type="containsText" dxfId="133" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="113" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H63))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9436,7 +9164,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H64">
-    <cfRule type="containsText" dxfId="132" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="112" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H64))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9591,7 +9319,7 @@
         <v>108</v>
       </c>
       <c r="I5" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5" t="str">
         <f>IF(OR(AND(I5&gt;1,I5&lt;&gt;"-")),"Can exchange","")</f>
@@ -9680,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="5" t="str">
-        <f t="shared" ref="J8:J63" si="0">IF(OR(AND(I8&gt;1,I8&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="J8:J60" si="0">IF(OR(AND(I8&gt;1,I8&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
       <c r="N8" s="23"/>
@@ -9741,7 +9469,7 @@
         <v>110</v>
       </c>
       <c r="I10" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
@@ -9869,7 +9597,7 @@
         <v>113</v>
       </c>
       <c r="I14" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="5" t="str">
         <f t="shared" si="0"/>
@@ -9901,7 +9629,7 @@
         <v>114</v>
       </c>
       <c r="I15" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="5" t="str">
         <f t="shared" si="0"/>
@@ -11356,7 +11084,7 @@
     <mergeCell ref="C1:G1"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
-  <conditionalFormatting sqref="I6 I10 I12 I14 I22 I24 I27 I31 I33 I35 I37 I39 I41 I43 I50 I52 I55 I45 I47:I48">
+  <conditionalFormatting sqref="I10 I6 I12 I14 I22 I24 I27 I31 I33 I35 I37 I39 I41 I43 I50 I52 I55 I45 I47:I48">
     <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11369,11 +11097,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6 I10 I12 I14 I22 I24 I27 I31 I33 I35 I37 I39 I41 I43 I50 I52 I55 I45 I47:I48">
-    <cfRule type="containsText" dxfId="130" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="111" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I13 I15 I23 I30 I32 I34 I36 I38 I40 I42 I49 I51 I54 I44 I46">
+  <conditionalFormatting sqref="I15 I13 I23 I30 I32 I34 I36 I38 I40 I42 I49 I51 I54 I44 I46">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11386,7 +11114,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13 I15 I23 I30 I32 I34 I36 I38 I40 I42 I49 I51 I54 I44 I46">
-    <cfRule type="containsText" dxfId="129" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="110" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11403,7 +11131,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:I9">
-    <cfRule type="containsText" dxfId="128" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="109" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11420,7 +11148,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I56">
-    <cfRule type="containsText" dxfId="127" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="108" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I56))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11437,7 +11165,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I53">
-    <cfRule type="containsText" dxfId="126" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="107" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11454,7 +11182,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I17">
-    <cfRule type="containsText" dxfId="125" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="106" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I17))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11471,7 +11199,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18">
-    <cfRule type="containsText" dxfId="124" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="105" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I18))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11488,7 +11216,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19">
-    <cfRule type="containsText" dxfId="123" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="104" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11505,7 +11233,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="122" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="103" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11522,7 +11250,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="containsText" dxfId="121" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="102" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11539,7 +11267,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="120" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="101" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11556,7 +11284,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11">
-    <cfRule type="containsText" dxfId="119" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="100" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I11))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11573,7 +11301,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16">
-    <cfRule type="containsText" dxfId="118" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="99" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I16))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11590,7 +11318,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I20">
-    <cfRule type="containsText" dxfId="117" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="98" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I20))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11607,7 +11335,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="containsText" dxfId="116" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="97" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I21))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11624,11 +11352,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25">
-    <cfRule type="containsText" dxfId="115" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="96" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I25))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I28 I26">
+  <conditionalFormatting sqref="I26 I28">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11641,7 +11369,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26 I28">
-    <cfRule type="containsText" dxfId="114" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="95" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11658,7 +11386,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29">
-    <cfRule type="containsText" dxfId="113" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="94" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11699,17 +11427,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I60">
-    <cfRule type="containsText" dxfId="110" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="93" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I60))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I59">
-    <cfRule type="containsText" dxfId="109" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="92" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I58">
-    <cfRule type="containsText" dxfId="108" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="91" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11726,7 +11454,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I57">
-    <cfRule type="containsText" dxfId="107" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="90" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I57))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11743,7 +11471,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I61">
-    <cfRule type="containsText" dxfId="106" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="89" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11760,7 +11488,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I62">
-    <cfRule type="containsText" dxfId="105" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="88" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I62))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11777,7 +11505,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63">
-    <cfRule type="containsText" dxfId="104" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="87" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I63))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11794,7 +11522,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I64">
-    <cfRule type="containsText" dxfId="103" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="86" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I64))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13695,7 +13423,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="I31 I33 I37 I39 I41 I43 I50 I52 I55 I45 I47:I48">
+  <conditionalFormatting sqref="I33 I31 I37 I39 I41 I43 I50 I52 I55 I45 I47:I48">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13708,11 +13436,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31 I33 I37 I39 I41 I43 I50 I52 I55 I45 I47:I48">
-    <cfRule type="containsText" dxfId="102" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="85" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I36 I32 I38 I40 I42 I49 I51 I54 I44 I46">
+  <conditionalFormatting sqref="I32 I36 I38 I40 I42 I49 I51 I54 I44 I46">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13725,7 +13453,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32 I36 I38 I40 I42 I49 I51 I54 I44 I46">
-    <cfRule type="containsText" dxfId="101" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="84" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13742,7 +13470,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18">
-    <cfRule type="containsText" dxfId="100" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="83" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I18))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13759,7 +13487,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I17">
-    <cfRule type="containsText" dxfId="99" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="82" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I17))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13776,7 +13504,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I53">
-    <cfRule type="containsText" dxfId="98" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="81" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13793,7 +13521,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19">
-    <cfRule type="containsText" dxfId="97" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="80" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13809,7 +13537,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4 I6 I8 I10 I12 I14 I16">
+  <conditionalFormatting sqref="I6 I4 I8 I10 I12 I14 I16">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13834,11 +13562,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="96" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="79" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3 I5 I9 I11 I15">
+  <conditionalFormatting sqref="I5 I3 I9 I11 I15">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13851,7 +13579,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I20">
-    <cfRule type="containsText" dxfId="95" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="78" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I20))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13868,12 +13596,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I27">
-    <cfRule type="containsText" dxfId="94" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="77" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I21))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="93" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="76" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13890,12 +13618,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3 I5 I9 I11 I15">
-    <cfRule type="containsText" dxfId="92" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="75" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4 I6 I8 I10 I12 I14 I16">
-    <cfRule type="containsText" dxfId="91" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="74" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13912,7 +13640,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28">
-    <cfRule type="containsText" dxfId="90" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="73" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13929,7 +13657,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29">
-    <cfRule type="containsText" dxfId="89" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="72" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13946,7 +13674,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30">
-    <cfRule type="containsText" dxfId="88" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="71" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13963,7 +13691,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="containsText" dxfId="87" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="70" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13980,7 +13708,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I35">
-    <cfRule type="containsText" dxfId="86" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="69" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14021,17 +13749,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I60">
-    <cfRule type="containsText" dxfId="83" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="68" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I59">
-    <cfRule type="containsText" dxfId="82" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="67" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I58">
-    <cfRule type="containsText" dxfId="81" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="66" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14048,7 +13776,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I56">
-    <cfRule type="containsText" dxfId="80" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="65" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I56))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14065,7 +13793,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I57">
-    <cfRule type="containsText" dxfId="79" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="64" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I57))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14082,7 +13810,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I61">
-    <cfRule type="containsText" dxfId="78" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="63" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14099,7 +13827,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I62">
-    <cfRule type="containsText" dxfId="77" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="62" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I62))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14116,7 +13844,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63">
-    <cfRule type="containsText" dxfId="76" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="61" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I63))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14133,7 +13861,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I64">
-    <cfRule type="containsText" dxfId="75" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="60" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I64))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15731,7 +15459,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="5" t="str">
-        <f t="shared" ref="G60:G63" si="4">IF(OR(AND(F60&gt;1,F60&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G60" si="4">IF(OR(AND(F60&gt;1,F60&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -15821,7 +15549,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F17 F19 F23 F25 F27 F29 F31 F33 F35 F37 F39 F41 F43 F45 F47 F49 F51 F53">
+  <conditionalFormatting sqref="F19 F17 F23 F25 F27 F29 F31 F33 F35 F37 F39 F41 F43 F45 F47 F49 F51 F53">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -15846,16 +15574,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17 F19 F23 F25 F27 F29 F31 F33 F35 F37 F39 F41 F43 F45 F47 F49 F51 F53">
-    <cfRule type="containsText" dxfId="74" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="59" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="containsText" dxfId="73" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="58" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20 F22 F24 F26 F28 F30 F32 F34 F36 F38 F40 F42 F44 F46 F48 F50 F52 F54">
+  <conditionalFormatting sqref="F22 F20 F24 F26 F28 F30 F32 F34 F36 F38 F40 F42 F44 F46 F48 F50 F52 F54">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -15868,7 +15596,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20 F22 F24 F26 F28 F30 F32 F34 F36 F38 F40 F42 F44 F46 F48 F50 F52 F54">
-    <cfRule type="containsText" dxfId="72" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="57" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15885,7 +15613,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21">
-    <cfRule type="containsText" dxfId="71" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="56" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15950,7 +15678,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57:F58">
-    <cfRule type="containsText" dxfId="70" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="55" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15967,7 +15695,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59">
-    <cfRule type="containsText" dxfId="69" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="54" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15984,17 +15712,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F60">
-    <cfRule type="containsText" dxfId="68" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="53" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F56">
-    <cfRule type="containsText" dxfId="67" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="52" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F56))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55">
-    <cfRule type="containsText" dxfId="66" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="51" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F55))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16011,17 +15739,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64">
-    <cfRule type="containsText" dxfId="61" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="50" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F64))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F61">
-    <cfRule type="containsText" dxfId="60" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="49" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62">
-    <cfRule type="containsText" dxfId="59" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="48" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F62))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16038,7 +15766,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="containsText" dxfId="58" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="47" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F63))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17674,7 +17402,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="5" t="str">
-        <f t="shared" ref="I56:I62" si="2">IF(OR(AND(H56&gt;1,H56&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I56:I59" si="2">IF(OR(AND(H56&gt;1,H56&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -17857,11 +17585,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H54">
-    <cfRule type="containsText" dxfId="56" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="46" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5 H11 H13 H15">
+  <conditionalFormatting sqref="H11 H5 H13 H15">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17873,7 +17601,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4 H12 H14 H16">
+  <conditionalFormatting sqref="H12 H4 H14 H16">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17886,16 +17614,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5 H11 H13 H15">
-    <cfRule type="containsText" dxfId="55" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="45" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4 H12 H14 H16">
-    <cfRule type="containsText" dxfId="54" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="44" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H32 H17 H34 H36 H38 H40 H42 H44 H48 H50 H52">
+  <conditionalFormatting sqref="H17 H32 H34 H36 H38 H40 H42 H44 H48 H50 H52">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17907,7 +17635,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18 H20 H33 H35 H37 H39 H41 H43 H49 H51">
+  <conditionalFormatting sqref="H20 H18 H33 H35 H37 H39 H41 H43 H49 H51">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17932,21 +17660,21 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19">
-    <cfRule type="containsText" dxfId="53" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="43" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17 H32 H34 H36 H38 H40 H42 H44 H48 H50 H52">
-    <cfRule type="containsText" dxfId="52" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="42" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18 H20 H33 H35 H37 H39 H41 H43 H49 H51">
-    <cfRule type="containsText" dxfId="51" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="41" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21 H23 H25 H27">
+  <conditionalFormatting sqref="H23 H21 H25 H27">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17959,11 +17687,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21 H23 H25 H27">
-    <cfRule type="containsText" dxfId="50" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="40" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22 H24 H26 H28">
+  <conditionalFormatting sqref="H24 H22 H26 H28">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17976,7 +17704,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22 H24 H26 H28">
-    <cfRule type="containsText" dxfId="49" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17993,7 +17721,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H56">
-    <cfRule type="containsText" dxfId="48" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18010,7 +17738,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H57">
-    <cfRule type="containsText" dxfId="47" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18027,7 +17755,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H58">
-    <cfRule type="containsText" dxfId="46" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18044,7 +17772,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H59">
-    <cfRule type="containsText" dxfId="45" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18073,7 +17801,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H55">
-    <cfRule type="containsText" dxfId="42" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H55))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18090,12 +17818,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H63">
-    <cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H63))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H60">
-    <cfRule type="containsText" dxfId="38" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18112,7 +17840,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H61">
-    <cfRule type="containsText" dxfId="37" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H61))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18129,7 +17857,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H62">
-    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H62))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19697,7 +19425,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="5" t="str">
-        <f t="shared" ref="H56:H62" si="2">IF(OR(AND(G56&gt;1,G56&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="H56:H59" si="2">IF(OR(AND(G56&gt;1,G56&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -19860,7 +19588,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G19 G21 G23 G25 G27:G28 G30 G32 G36 G38 G40 G42 G46 G48 G50">
+  <conditionalFormatting sqref="G21 G19 G23 G25 G27:G28 G30 G32 G36 G38 G40 G42 G46 G48 G50">
     <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -19885,16 +19613,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19 G21 G23 G25 G27:G28 G30 G32 G36 G38 G40 G42 G46 G48 G50">
-    <cfRule type="containsText" dxfId="34" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G18">
-    <cfRule type="containsText" dxfId="33" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G20 G22 G24 G26 G29 G31 G35 G37 G39 G41 G43 G47 G49 G51 G45 G53">
+  <conditionalFormatting sqref="G22 G20 G24 G26 G29 G31 G35 G37 G39 G41 G43 G47 G49 G51 G45 G53">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -19907,7 +19635,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G20 G22 G24 G26 G29 G31 G35 G37 G39 G41 G43 G47 G49 G51 G45 G53">
-    <cfRule type="containsText" dxfId="32" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19924,7 +19652,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G44">
-    <cfRule type="containsText" dxfId="31" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19953,12 +19681,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G55">
-    <cfRule type="containsText" dxfId="30" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="25" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33">
-    <cfRule type="containsText" dxfId="29" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19975,7 +19703,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="containsText" dxfId="28" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19992,7 +19720,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G52">
-    <cfRule type="containsText" dxfId="27" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20009,7 +19737,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G54">
-    <cfRule type="containsText" dxfId="26" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20050,12 +19778,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G57">
-    <cfRule type="containsText" dxfId="25" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59">
-    <cfRule type="containsText" dxfId="24" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20072,7 +19800,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56">
-    <cfRule type="containsText" dxfId="23" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20089,7 +19817,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G58">
-    <cfRule type="containsText" dxfId="22" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20118,12 +19846,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G60">
-    <cfRule type="containsText" dxfId="18" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G61">
-    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G61))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20140,12 +19868,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G63">
-    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G63))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G62">
-    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21818,7 +21546,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="5" t="str">
-        <f t="shared" ref="H56:H60" si="4">IF(OR(AND(G56&gt;1,G56&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="H56:H57" si="4">IF(OR(AND(G56&gt;1,G56&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
       <c r="K56" s="23"/>
@@ -21960,7 +21688,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G33 G35 G37 G39 G41 G44 G46 G48 G50 G52">
+  <conditionalFormatting sqref="G35 G33 G37 G39 G41 G44 G46 G48 G50 G52">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -21972,7 +21700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G32 G34 G36 G38 G40 G42:G43 G45 G47 G49 G51">
+  <conditionalFormatting sqref="G34 G32 G36 G38 G40 G42:G43 G45 G47 G49 G51">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -21985,12 +21713,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33 G35 G37 G39 G41 G44 G46 G48 G50 G52">
-    <cfRule type="containsText" dxfId="13" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32 G34 G36 G38 G40 G42:G43 G45 G47 G49 G51">
-    <cfRule type="containsText" dxfId="12" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22007,7 +21735,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53">
-    <cfRule type="containsText" dxfId="11" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G53))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22036,12 +21764,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G57">
-    <cfRule type="containsText" dxfId="10" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56">
-    <cfRule type="containsText" dxfId="9" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22058,7 +21786,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G54:G55">
-    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G54))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22075,7 +21803,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G58">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22092,7 +21820,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G59))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22109,7 +21837,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G60">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G60))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22126,7 +21854,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G61">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G61))))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Collections/United_Kingdom/#United_Kingdom#After_DecimalDay#Regular#[1968-present]#circulation_quality.xlsx
+++ b/Collections/United_Kingdom/#United_Kingdom#After_DecimalDay#Regular#[1968-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\United_Kingdom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35218AC8-0F76-4778-AB5B-3B13645A318F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A7CA74-341C-4054-A349-FC96F0C5A195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="halfpence" sheetId="26" r:id="rId1"/>
@@ -3850,7 +3850,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5087,7 +5087,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F8 F6 F10 F12 F14 F16 F18">
+  <conditionalFormatting sqref="F6 F8 F10 F12 F14 F16 F18">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5104,7 +5104,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11 F9 F13 F15 F17">
+  <conditionalFormatting sqref="F9 F11 F13 F15 F17">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6219,7 +6219,7 @@
         <v>47</v>
       </c>
       <c r="H38" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="5" t="str">
         <f t="shared" si="0"/>
@@ -6848,7 +6848,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H8 H6 H10 H12 H14 H16 H18 H20 H22 H24 H26 H29 H31 H33 H35 H37 H39 H41 H43 H50 H52 H55 H45 H47:H48">
+  <conditionalFormatting sqref="H6 H8 H10 H12 H14 H16 H18 H20 H22 H24 H26 H29 H31 H33 H35 H37 H39 H41 H43 H50 H52 H55 H45 H47:H48">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6865,7 +6865,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11 H9 H13 H15 H17 H19 H21 H23 H25 H30 H32 H34 H36 H38 H40 H42 H49 H51 H54 H44 H46">
+  <conditionalFormatting sqref="H9 H11 H13 H15 H17 H19 H21 H23 H25 H30 H32 H34 H36 H38 H40 H42 H49 H51 H54 H44 H46">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7854,7 +7854,7 @@
         <v>80</v>
       </c>
       <c r="H28" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8010,7 +8010,7 @@
         <v>85</v>
       </c>
       <c r="H33" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8857,7 +8857,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H10 H6 H12 H14 H16 H20 H22 H24 H26 H29 H31 H33 H36 H38 H40 H42 H44 H51 H53 H56 H46 H48:H49">
+  <conditionalFormatting sqref="H6 H10 H12 H14 H16 H20 H22 H24 H26 H29 H31 H33 H36 H38 H40 H42 H44 H51 H53 H56 H46 H48:H49">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8874,7 +8874,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13 H11 H15 H21 H23 H25 H30 H32 H35 H37 H39 H41 H43 H50 H52 H55 H45 H47">
+  <conditionalFormatting sqref="H11 H13 H15 H21 H23 H25 H30 H32 H35 H37 H39 H41 H43 H50 H52 H55 H45 H47">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9998,7 +9998,7 @@
         <v>119</v>
       </c>
       <c r="I27" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="5" t="str">
         <f t="shared" si="0"/>
@@ -10482,7 +10482,7 @@
         <v>133</v>
       </c>
       <c r="I42" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="5" t="str">
         <f t="shared" si="0"/>
@@ -11084,7 +11084,7 @@
     <mergeCell ref="C1:G1"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
-  <conditionalFormatting sqref="I10 I6 I12 I14 I22 I24 I27 I31 I33 I35 I37 I39 I41 I43 I50 I52 I55 I45 I47:I48">
+  <conditionalFormatting sqref="I6 I10 I12 I14 I22 I24 I27 I31 I33 I35 I37 I39 I41 I43 I50 I52 I55 I45 I47:I48">
     <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11101,7 +11101,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I15 I13 I23 I30 I32 I34 I36 I38 I40 I42 I49 I51 I54 I44 I46">
+  <conditionalFormatting sqref="I13 I15 I23 I30 I32 I34 I36 I38 I40 I42 I49 I51 I54 I44 I46">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11356,7 +11356,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(I25))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26 I28">
+  <conditionalFormatting sqref="I28 I26">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13423,7 +13423,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="I33 I31 I37 I39 I41 I43 I50 I52 I55 I45 I47:I48">
+  <conditionalFormatting sqref="I31 I33 I37 I39 I41 I43 I50 I52 I55 I45 I47:I48">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13440,7 +13440,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I32 I36 I38 I40 I42 I49 I51 I54 I44 I46">
+  <conditionalFormatting sqref="I36 I32 I38 I40 I42 I49 I51 I54 I44 I46">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13537,7 +13537,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6 I4 I8 I10 I12 I14 I16">
+  <conditionalFormatting sqref="I4 I6 I8 I10 I12 I14 I16">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13566,7 +13566,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5 I3 I9 I11 I15">
+  <conditionalFormatting sqref="I3 I5 I9 I11 I15">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -15549,7 +15549,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F19 F17 F23 F25 F27 F29 F31 F33 F35 F37 F39 F41 F43 F45 F47 F49 F51 F53">
+  <conditionalFormatting sqref="F17 F19 F23 F25 F27 F29 F31 F33 F35 F37 F39 F41 F43 F45 F47 F49 F51 F53">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -15583,7 +15583,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22 F20 F24 F26 F28 F30 F32 F34 F36 F38 F40 F42 F44 F46 F48 F50 F52 F54">
+  <conditionalFormatting sqref="F20 F22 F24 F26 F28 F30 F32 F34 F36 F38 F40 F42 F44 F46 F48 F50 F52 F54">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17589,7 +17589,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11 H5 H13 H15">
+  <conditionalFormatting sqref="H5 H11 H13 H15">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17601,7 +17601,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12 H4 H14 H16">
+  <conditionalFormatting sqref="H4 H12 H14 H16">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17623,7 +17623,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17 H32 H34 H36 H38 H40 H42 H44 H48 H50 H52">
+  <conditionalFormatting sqref="H32 H17 H34 H36 H38 H40 H42 H44 H48 H50 H52">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17635,7 +17635,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20 H18 H33 H35 H37 H39 H41 H43 H49 H51">
+  <conditionalFormatting sqref="H18 H20 H33 H35 H37 H39 H41 H43 H49 H51">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17674,7 +17674,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23 H21 H25 H27">
+  <conditionalFormatting sqref="H21 H23 H25 H27">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -17691,7 +17691,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(H21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24 H22 H26 H28">
+  <conditionalFormatting sqref="H22 H24 H26 H28">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -19588,7 +19588,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G21 G19 G23 G25 G27:G28 G30 G32 G36 G38 G40 G42 G46 G48 G50">
+  <conditionalFormatting sqref="G19 G21 G23 G25 G27:G28 G30 G32 G36 G38 G40 G42 G46 G48 G50">
     <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -19622,7 +19622,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22 G20 G24 G26 G29 G31 G35 G37 G39 G41 G43 G47 G49 G51 G45 G53">
+  <conditionalFormatting sqref="G20 G22 G24 G26 G29 G31 G35 G37 G39 G41 G43 G47 G49 G51 G45 G53">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -21688,7 +21688,7 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G35 G33 G37 G39 G41 G44 G46 G48 G50 G52">
+  <conditionalFormatting sqref="G33 G35 G37 G39 G41 G44 G46 G48 G50 G52">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -21700,7 +21700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G34 G32 G36 G38 G40 G42:G43 G45 G47 G49 G51">
+  <conditionalFormatting sqref="G32 G34 G36 G38 G40 G42:G43 G45 G47 G49 G51">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
